--- a/29-06-2026/student.xlsx
+++ b/29-06-2026/student.xlsx
@@ -1,28 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RwLectures\Python\29-06-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD460E82-2C50-4862-ACCA-0A39BA8FED86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B29C572-CED4-42DF-86C5-8011930065B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="9" r:id="rId7"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -100,13 +106,31 @@
   </si>
   <si>
     <t>English</t>
+  </si>
+  <si>
+    <t>Sum of No</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Marks</t>
+  </si>
+  <si>
+    <t>Sum of Age</t>
+  </si>
+  <si>
+    <t>(blank)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,8 +146,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +164,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -164,13 +201,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -187,6 +237,362 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="vivek kachhadiya" refreshedDate="46209.670373611109" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{08C32937-B26A-4E43-AD75-17ABE729500F}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:C7" sheet="Sheet2"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="No" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="6"/>
+    </cacheField>
+    <cacheField name="Subject" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Maths"/>
+        <s v="Chemistry"/>
+        <s v="Physics"/>
+        <s v="Biology"/>
+        <s v="Social Science"/>
+        <s v="English"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Marks" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="100" maxValue="100"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="vivek kachhadiya" refreshedDate="46209.670770254626" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{60968994-6FB0-4F9F-A1F1-6EC72C2BB0AD}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E8" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Vivek"/>
+        <s v="Rahul"/>
+        <s v="Neha"/>
+        <s v="Priya"/>
+        <s v="Zeel"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="21" maxValue="50"/>
+    </cacheField>
+    <cacheField name="Marks" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="78" maxValue="91"/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="Surat"/>
+        <s v="Vadodara"/>
+        <m/>
+        <s v="Rajkot"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="JoiningDate" numFmtId="0">
+      <sharedItems count="5">
+        <s v="15-06-2026"/>
+        <s v="20-05-2025"/>
+        <s v="20-06-2024"/>
+        <s v="01-02-2023"/>
+        <s v="01-05-2026"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <n v="100"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="7">
+  <r>
+    <x v="0"/>
+    <n v="28"/>
+    <n v="89"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="28"/>
+    <n v="89"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="25"/>
+    <n v="78"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="21"/>
+    <n v="91"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="23"/>
+    <m/>
+    <x v="2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="50"/>
+    <n v="89"/>
+    <x v="3"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="28"/>
+    <n v="89"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C9BD242-CDF4-4B4C-A9E0-523979FF1BF4}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="0"/>
+    <field x="3"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Age" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Marks" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C34178A-4036-4404-9806-A11DB636B311}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of No" fld="0" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Marks" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -473,150 +879,459 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8736A11D-18C6-44B3-9077-0C8C6612CCE4}">
+  <dimension ref="A3:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5">
+        <v>84</v>
+      </c>
+      <c r="C13" s="5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="5">
+        <v>84</v>
+      </c>
+      <c r="C14" s="5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5">
+        <v>84</v>
+      </c>
+      <c r="C15" s="5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5">
+        <v>50</v>
+      </c>
+      <c r="C16" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <v>50</v>
+      </c>
+      <c r="C18" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="5">
+        <v>203</v>
+      </c>
+      <c r="C19" s="5">
+        <v>525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>28</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>89</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>28</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>89</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>25</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>78</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>21</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>91</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>50</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>89</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>28</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>89</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="F8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A41A02-D83C-4287-AA50-26AA1253C134}">
+  <dimension ref="A3:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="5">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="5">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="5">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5">
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A62728-20A5-40EE-838F-8B76D70ACD8B}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -707,7 +1422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5457B2-066C-48FD-9DDE-2427298A6697}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
